--- a/output/pdf_financials_xlsx/TF.xlsx
+++ b/output/pdf_financials_xlsx/TF.xlsx
@@ -2342,13 +2342,13 @@
         <v>2.832</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.802</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>13.303</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="35">
@@ -2422,13 +2422,13 @@
         <v>2.832</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.802</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>13.303</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="37">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">

--- a/output/pdf_financials_xlsx/TF.xlsx
+++ b/output/pdf_financials_xlsx/TF.xlsx
@@ -5878,10 +5878,10 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>60.314</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>10.543</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -37709,7 +37709,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TF.xlsx
+++ b/output/pdf_financials_xlsx/TF.xlsx
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0</v>
+        <v>-36.533</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -5681,7 +5681,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>36.625</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -5915,31 +5915,31 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.331</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-0.338</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-23.592</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.416</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-3.693</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-12.181</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-5.875</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-7.074</v>
       </c>
     </row>
     <row r="122">
@@ -31077,7 +31077,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -36875,7 +36879,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -36946,7 +36954,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
